--- a/backend/temp/test1.xlsx
+++ b/backend/temp/test1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63332D25-080F-4E33-83A5-CD214E7EBD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5BD1F5-8F5A-4792-9CB8-FFA657AAD3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB21051E-8046-46A4-BAEA-8D3DDE1B2D3C}"/>
+    <workbookView xWindow="708" yWindow="252" windowWidth="17976" windowHeight="11076" xr2:uid="{DB21051E-8046-46A4-BAEA-8D3DDE1B2D3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="217">
   <si>
     <t>MATUnit</t>
   </si>
@@ -95,12 +95,6 @@
     <t>ชิ้น</t>
   </si>
   <si>
-    <t>BP1131-I-R (ชิ้น): BP1131-I-R (ชิ้น)</t>
-  </si>
-  <si>
-    <t>BP1132-I-R (ชิ้น): BP1132-I-R (ชิ้น)</t>
-  </si>
-  <si>
     <t>08000000000P1O</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
     <t>C01-CPI-ST03-A-103</t>
   </si>
   <si>
-    <t>28/05/62</t>
-  </si>
-  <si>
     <t>08000000000P1P</t>
   </si>
   <si>
@@ -122,9 +113,6 @@
     <t>C01-CPI-ST03-01</t>
   </si>
   <si>
-    <t>26/12/62</t>
-  </si>
-  <si>
     <t>08000000000P1Q</t>
   </si>
   <si>
@@ -176,9 +164,6 @@
     <t>Branch No.</t>
   </si>
   <si>
-    <t>A:B</t>
-  </si>
-  <si>
     <t>08000000000P2V</t>
   </si>
   <si>
@@ -188,13 +173,520 @@
     <t>C01-CPI-ST03-02</t>
   </si>
   <si>
-    <t>C:D</t>
-  </si>
-  <si>
     <t>08000000000P3V</t>
   </si>
   <si>
     <t>C01-CPI-ST03-03</t>
+  </si>
+  <si>
+    <t>MAT001:Steel Rod</t>
+  </si>
+  <si>
+    <t>MAT002:Copper Wire</t>
+  </si>
+  <si>
+    <t>MAT003:Aluminum Sheet</t>
+  </si>
+  <si>
+    <t>MAT004:Plastic Pellet</t>
+  </si>
+  <si>
+    <t>MAT005:Rubber Tube</t>
+  </si>
+  <si>
+    <t>MAT006:Glass Panel</t>
+  </si>
+  <si>
+    <t>MAT007:Iron Plate</t>
+  </si>
+  <si>
+    <t>MAT008:Wooden Plank</t>
+  </si>
+  <si>
+    <t>MAT009:Textile Fabric</t>
+  </si>
+  <si>
+    <t>MAT010:Cardboard Box</t>
+  </si>
+  <si>
+    <t>MAT011:Brass Bolt</t>
+  </si>
+  <si>
+    <t>MAT012:Silicone Sealant</t>
+  </si>
+  <si>
+    <t>MAT013:Carbon Fiber</t>
+  </si>
+  <si>
+    <t>MAT014:Foam Block</t>
+  </si>
+  <si>
+    <t>MAT015:Ceramic Tile</t>
+  </si>
+  <si>
+    <t>MAT016:Nylon Rope</t>
+  </si>
+  <si>
+    <t>MAT017:PVC Pipe</t>
+  </si>
+  <si>
+    <t>MAT018:Zinc Coating</t>
+  </si>
+  <si>
+    <t>MAT019:Paper Roll</t>
+  </si>
+  <si>
+    <t>08000000000P4A</t>
+  </si>
+  <si>
+    <t>08000000000P4B</t>
+  </si>
+  <si>
+    <t>08000000000P5A</t>
+  </si>
+  <si>
+    <t>08000000000P5B</t>
+  </si>
+  <si>
+    <t>08000000000P5C</t>
+  </si>
+  <si>
+    <t>08000000000P5V</t>
+  </si>
+  <si>
+    <t>08000000000P6A</t>
+  </si>
+  <si>
+    <t>08000000000P7A</t>
+  </si>
+  <si>
+    <t>08000000000P8C</t>
+  </si>
+  <si>
+    <t>08000000000P9A</t>
+  </si>
+  <si>
+    <t>08000000000A10</t>
+  </si>
+  <si>
+    <t>08000000000A11</t>
+  </si>
+  <si>
+    <t>08000000000A12</t>
+  </si>
+  <si>
+    <t>08000000000B1A</t>
+  </si>
+  <si>
+    <t>08000000000C7Z</t>
+  </si>
+  <si>
+    <t>08000000000C7Y</t>
+  </si>
+  <si>
+    <t>08000000000F6A</t>
+  </si>
+  <si>
+    <t>08000000000F6B</t>
+  </si>
+  <si>
+    <t>08000000000F6C</t>
+  </si>
+  <si>
+    <t>08000000000F6D</t>
+  </si>
+  <si>
+    <t>08000000000G7A</t>
+  </si>
+  <si>
+    <t>2212INC000016 #11</t>
+  </si>
+  <si>
+    <t>2212INC000016 #12</t>
+  </si>
+  <si>
+    <t>2212INC000016 #13</t>
+  </si>
+  <si>
+    <t>2212INC000016 #14</t>
+  </si>
+  <si>
+    <t>2212INC000016 #15</t>
+  </si>
+  <si>
+    <t>2212INC000016 #16</t>
+  </si>
+  <si>
+    <t>2212INC000016 #17</t>
+  </si>
+  <si>
+    <t>2212INC000016 #18</t>
+  </si>
+  <si>
+    <t>2212INC000016 #19</t>
+  </si>
+  <si>
+    <t>2212INC000016 #20</t>
+  </si>
+  <si>
+    <t>2212INC000016 #21</t>
+  </si>
+  <si>
+    <t>2212INC000016 #22</t>
+  </si>
+  <si>
+    <t>2212INC000016 #23</t>
+  </si>
+  <si>
+    <t>2212INC000016 #24</t>
+  </si>
+  <si>
+    <t>2212INC000016 #25</t>
+  </si>
+  <si>
+    <t>2212INC000016 #26</t>
+  </si>
+  <si>
+    <t>2212INC000016 #27</t>
+  </si>
+  <si>
+    <t>2212INC000016 #28</t>
+  </si>
+  <si>
+    <t>2212INC000016 #29</t>
+  </si>
+  <si>
+    <t>2212INC000016 #30</t>
+  </si>
+  <si>
+    <t>2212INC000016 #31</t>
+  </si>
+  <si>
+    <t>2212INC000016 #32</t>
+  </si>
+  <si>
+    <t>2212INC000016 #33</t>
+  </si>
+  <si>
+    <t>2212INC000016 #34</t>
+  </si>
+  <si>
+    <t>2212INC000016 #35</t>
+  </si>
+  <si>
+    <t>2212INC000016 #36</t>
+  </si>
+  <si>
+    <t>2212INC000016 #37</t>
+  </si>
+  <si>
+    <t>2212INC000016 #38</t>
+  </si>
+  <si>
+    <t>2212INC000016 #39</t>
+  </si>
+  <si>
+    <t>2212INC000016 #40</t>
+  </si>
+  <si>
+    <t>2212INC000016 #41</t>
+  </si>
+  <si>
+    <t>2212INC000016 #42</t>
+  </si>
+  <si>
+    <t>2212INC000016 #43</t>
+  </si>
+  <si>
+    <t>2212INC000016 #44</t>
+  </si>
+  <si>
+    <t>2212INC000016 #45</t>
+  </si>
+  <si>
+    <t>2212INC000016 #46</t>
+  </si>
+  <si>
+    <t>2212INC000016 #47</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-04</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-05</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-06</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-07</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-08</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-09</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-10</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-11</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-12</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-13</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-14</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-15</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-16</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-17</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-18</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-19</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-20</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-21</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-22</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-23</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-24</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-25</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-26</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-27</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-28</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-29</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-30</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-31</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-32</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-33</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-34</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-35</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-36</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-37</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-38</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-39</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-40</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-00</t>
+  </si>
+  <si>
+    <t>08000000000A13</t>
+  </si>
+  <si>
+    <t>2212INC000016 #48</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-41</t>
+  </si>
+  <si>
+    <t>2212INC000016 #49</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-42</t>
+  </si>
+  <si>
+    <t>2212INC000016 #50</t>
+  </si>
+  <si>
+    <t>C01-CPI-ST03-43</t>
+  </si>
+  <si>
+    <t>08000000000P1S</t>
+  </si>
+  <si>
+    <t>08000000000P1V</t>
+  </si>
+  <si>
+    <t>08000000000P4C</t>
+  </si>
+  <si>
+    <t>08000000000P4D</t>
+  </si>
+  <si>
+    <t>08000000000P6B</t>
+  </si>
+  <si>
+    <t>08000000000P6C</t>
+  </si>
+  <si>
+    <t>08000000000P6D</t>
+  </si>
+  <si>
+    <t>08000000000P7B</t>
+  </si>
+  <si>
+    <t>08000000000P7C</t>
+  </si>
+  <si>
+    <t>08000000000P7D</t>
+  </si>
+  <si>
+    <t>08000000000P8A</t>
+  </si>
+  <si>
+    <t>08000000000P8B</t>
+  </si>
+  <si>
+    <t>08000000000P8D</t>
+  </si>
+  <si>
+    <t>08000000000P9B</t>
+  </si>
+  <si>
+    <t>08000000000P9C</t>
+  </si>
+  <si>
+    <t>08000000000P9D</t>
+  </si>
+  <si>
+    <t>08000000000B1B</t>
+  </si>
+  <si>
+    <t>08000000000B1C</t>
+  </si>
+  <si>
+    <t>08000000000B1D</t>
+  </si>
+  <si>
+    <t>08000000000C7W</t>
+  </si>
+  <si>
+    <t>08000000000C7X</t>
+  </si>
+  <si>
+    <t>08000000000D10</t>
+  </si>
+  <si>
+    <t>08000000000D11</t>
+  </si>
+  <si>
+    <t>08000000000D12</t>
+  </si>
+  <si>
+    <t>08000000000D13</t>
+  </si>
+  <si>
+    <t>08000000000G7B</t>
+  </si>
+  <si>
+    <t>08000000000G7C</t>
+  </si>
+  <si>
+    <t>08000000000G7D</t>
+  </si>
+  <si>
+    <t>08000000000L67</t>
+  </si>
+  <si>
+    <t>08000000000L68</t>
+  </si>
+  <si>
+    <t>08000000000L69</t>
+  </si>
+  <si>
+    <t>08000000000L70</t>
+  </si>
+  <si>
+    <t>08000000000A3A</t>
+  </si>
+  <si>
+    <t>08000000000A4B</t>
+  </si>
+  <si>
+    <t>08000000000A4C</t>
+  </si>
+  <si>
+    <t>08000000000A4E</t>
+  </si>
+  <si>
+    <t>08000000000J3A</t>
+  </si>
+  <si>
+    <t>08000000000J3B</t>
+  </si>
+  <si>
+    <t>08000000000J3C</t>
+  </si>
+  <si>
+    <t>08000000000J3E</t>
+  </si>
+  <si>
+    <t>08000000000E3A</t>
+  </si>
+  <si>
+    <t>08000000000E3B</t>
+  </si>
+  <si>
+    <t>08000000000E3C</t>
+  </si>
+  <si>
+    <t>08000000000E3D</t>
+  </si>
+  <si>
+    <t>08000000000K3A</t>
+  </si>
+  <si>
+    <t>08000000000K3B</t>
+  </si>
+  <si>
+    <t>08000000000K3C</t>
+  </si>
+  <si>
+    <t>08000000000K3F</t>
   </si>
 </sst>
 </file>
@@ -216,12 +708,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -236,13 +734,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,69 +1086,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DCADB9-8C5D-4C8A-A1F3-09A9EEBF6317}">
-  <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T82"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.296875" customWidth="1"/>
-    <col min="2" max="2" width="33.796875" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D3" s="4">
+        <v>105537000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="5">
-        <v>105537000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
       <c r="H4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -695,350 +1205,4317 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="7">
+        <v>24416</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3">
-        <v>22830</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
+      <c r="N6" s="9">
+        <v>1000.85</v>
+      </c>
+      <c r="O6" s="8">
+        <v>60</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7">
+        <v>24418</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>1</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>1</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="7">
+        <v>24417</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" s="4">
-        <v>1000.85</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="F8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="7">
+        <v>24420</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>1</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="7">
+        <v>24419</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="E10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8">
+        <v>1</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>1</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="3">
+        <v>24424</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T11" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3">
+        <v>24422</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" t="s">
+        <v>18</v>
+      </c>
+      <c r="T12" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3">
+        <v>24421</v>
+      </c>
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="3">
-        <v>22960</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="I9">
+      <c r="I13">
         <v>2</v>
       </c>
-      <c r="J9">
+      <c r="J13">
         <v>2</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>2</v>
       </c>
-      <c r="M9">
+      <c r="M13">
         <v>2</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3">
-        <v>24732</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>18</v>
+      </c>
+      <c r="T13" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="B14" s="3">
+        <v>24423</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>1</v>
+      </c>
+      <c r="R14" t="s">
+        <v>18</v>
+      </c>
+      <c r="T14" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" s="8" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1">
-        <v>1</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1</v>
-      </c>
-      <c r="R10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B15" s="7">
+        <v>24427</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>1</v>
+      </c>
+      <c r="N15" s="11">
+        <v>1</v>
+      </c>
+      <c r="O15" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>1</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="7">
+        <v>24426</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="10">
+        <v>1</v>
+      </c>
+      <c r="I16" s="10">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>1</v>
+      </c>
+      <c r="N16" s="11">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T16" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="7">
+        <v>24425</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="11">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8">
+        <v>10</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>1</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="7">
+        <v>24428</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="8">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10">
+        <v>1</v>
+      </c>
+      <c r="N18" s="11">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>1</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T18" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="3">
-        <v>24733</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B19" s="3">
+        <v>24430</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1000</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>1</v>
+      </c>
+      <c r="R19" t="s">
+        <v>18</v>
+      </c>
+      <c r="T19" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="3">
+        <v>24429</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>542</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>1</v>
+      </c>
+      <c r="R20" t="s">
+        <v>18</v>
+      </c>
+      <c r="T20" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3">
+        <v>24431</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1000</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>1</v>
+      </c>
+      <c r="R21" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3">
+        <v>24432</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B23" s="7">
+        <v>24436</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>1</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="10">
+        <v>1</v>
+      </c>
+      <c r="N23" s="11">
+        <v>1</v>
+      </c>
+      <c r="O23" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>1</v>
+      </c>
+      <c r="R23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T23" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="7">
+        <v>24435</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1</v>
+      </c>
+      <c r="H24" s="10">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10">
+        <v>1</v>
+      </c>
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8">
+        <v>0</v>
+      </c>
+      <c r="M24" s="10">
+        <v>1</v>
+      </c>
+      <c r="N24" s="11">
+        <v>1</v>
+      </c>
+      <c r="O24" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>1</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="7">
+        <v>24433</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="8">
+        <v>1</v>
+      </c>
+      <c r="H25" s="10">
+        <v>1</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="10">
+        <v>1</v>
+      </c>
+      <c r="N25" s="11">
+        <v>1</v>
+      </c>
+      <c r="O25" s="10">
+        <v>647</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>1</v>
+      </c>
+      <c r="R25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T25" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="7">
+        <v>24434</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10">
+        <v>1</v>
+      </c>
+      <c r="N26" s="11">
+        <v>1</v>
+      </c>
+      <c r="O26" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>1</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>1</v>
-      </c>
-      <c r="R11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="1"/>
-      <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="B27" s="3">
+        <v>24439</v>
+      </c>
+      <c r="C27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>1</v>
+      </c>
+      <c r="R27" t="s">
+        <v>18</v>
+      </c>
+      <c r="T27" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="3">
+        <v>24437</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
+        <v>349</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>1</v>
+      </c>
+      <c r="R28" t="s">
+        <v>18</v>
+      </c>
+      <c r="T28" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="3">
+        <v>24438</v>
+      </c>
+      <c r="C29" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>1</v>
+      </c>
+      <c r="R29" t="s">
+        <v>18</v>
+      </c>
+      <c r="T29" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="3">
+        <v>24440</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1</v>
+      </c>
+      <c r="R30" t="s">
+        <v>18</v>
+      </c>
+      <c r="T30" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="7">
+        <v>24441</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" s="8">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1</v>
+      </c>
+      <c r="J31" s="10">
+        <v>1</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10">
+        <v>1</v>
+      </c>
+      <c r="N31" s="11">
+        <v>1</v>
+      </c>
+      <c r="O31" s="10">
+        <v>645</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>1</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="7">
+        <v>24442</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10">
+        <v>1</v>
+      </c>
+      <c r="I32" s="10">
+        <v>1</v>
+      </c>
+      <c r="J32" s="10">
+        <v>1</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10">
+        <v>1</v>
+      </c>
+      <c r="N32" s="11">
+        <v>1</v>
+      </c>
+      <c r="O32" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>1</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="7">
+        <v>24443</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" s="8">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10">
+        <v>1</v>
+      </c>
+      <c r="I33" s="10">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10">
+        <v>1</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="10">
+        <v>1</v>
+      </c>
+      <c r="N33" s="11">
+        <v>1</v>
+      </c>
+      <c r="O33" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>1</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T33" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="7">
+        <v>24444</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="8">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10">
+        <v>1</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10">
+        <v>1</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10">
+        <v>1</v>
+      </c>
+      <c r="N34" s="11">
+        <v>1</v>
+      </c>
+      <c r="O34" s="10">
+        <v>2000</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>1</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T34" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="3">
+        <v>24446</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="2">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1">
+        <v>3000</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>1</v>
+      </c>
+      <c r="R35" t="s">
+        <v>18</v>
+      </c>
+      <c r="T35" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="3">
+        <v>24448</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1">
+        <v>3000</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>18</v>
+      </c>
+      <c r="T36" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="3">
+        <v>24445</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1">
+        <v>98</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>1</v>
+      </c>
+      <c r="R37" t="s">
+        <v>18</v>
+      </c>
+      <c r="T37" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="3">
+        <v>24447</v>
+      </c>
+      <c r="C38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>3000</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>1</v>
+      </c>
+      <c r="R38" t="s">
+        <v>18</v>
+      </c>
+      <c r="T38" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="7">
+        <v>24450</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="8">
+        <v>1</v>
+      </c>
+      <c r="H39" s="10">
+        <v>1</v>
+      </c>
+      <c r="I39" s="10">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10">
+        <v>1</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <v>0</v>
+      </c>
+      <c r="M39" s="10">
+        <v>1</v>
+      </c>
+      <c r="N39" s="11">
+        <v>1</v>
+      </c>
+      <c r="O39" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P39" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>1</v>
+      </c>
+      <c r="R39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T39" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="7">
+        <v>24452</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G40" s="8">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10">
+        <v>1</v>
+      </c>
+      <c r="I40" s="10">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10">
+        <v>1</v>
+      </c>
+      <c r="K40" s="8">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10">
+        <v>1</v>
+      </c>
+      <c r="N40" s="11">
+        <v>1</v>
+      </c>
+      <c r="O40" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P40" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="10">
+        <v>1</v>
+      </c>
+      <c r="R40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T40" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="7">
+        <v>24449</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="8">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10">
+        <v>1</v>
+      </c>
+      <c r="I41" s="10">
+        <v>1</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0</v>
+      </c>
+      <c r="M41" s="10">
+        <v>1</v>
+      </c>
+      <c r="N41" s="11">
+        <v>1</v>
+      </c>
+      <c r="O41" s="10">
+        <v>69</v>
+      </c>
+      <c r="P41" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>1</v>
+      </c>
+      <c r="R41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="7">
+        <v>24451</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G42" s="8">
+        <v>1</v>
+      </c>
+      <c r="H42" s="10">
+        <v>1</v>
+      </c>
+      <c r="I42" s="10">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10">
+        <v>1</v>
+      </c>
+      <c r="K42" s="8">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8">
+        <v>0</v>
+      </c>
+      <c r="M42" s="10">
+        <v>1</v>
+      </c>
+      <c r="N42" s="11">
+        <v>1</v>
+      </c>
+      <c r="O42" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P42" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>1</v>
+      </c>
+      <c r="R42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T42" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="3">
+        <v>24454</v>
+      </c>
+      <c r="C43" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" t="s">
+        <v>144</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2">
+        <v>1</v>
+      </c>
+      <c r="O43" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>1</v>
+      </c>
+      <c r="R43" t="s">
+        <v>18</v>
+      </c>
+      <c r="T43" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="3">
+        <v>24453</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2">
+        <v>1</v>
+      </c>
+      <c r="O44" s="1">
+        <v>55</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>1</v>
+      </c>
+      <c r="R44" t="s">
+        <v>18</v>
+      </c>
+      <c r="T44" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="3">
+        <v>24456</v>
+      </c>
+      <c r="C45" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45" t="s">
+        <v>109</v>
+      </c>
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2">
+        <v>1</v>
+      </c>
+      <c r="O45" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>18</v>
+      </c>
+      <c r="T45" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="3">
+        <v>24455</v>
+      </c>
+      <c r="C46" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2">
+        <v>1</v>
+      </c>
+      <c r="O46" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>1</v>
+      </c>
+      <c r="R46" t="s">
+        <v>18</v>
+      </c>
+      <c r="T46" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="7">
+        <v>24457</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="8">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10">
+        <v>1</v>
+      </c>
+      <c r="I47" s="10">
+        <v>1</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
+      <c r="K47" s="8">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <v>0</v>
+      </c>
+      <c r="M47" s="10">
+        <v>1</v>
+      </c>
+      <c r="N47" s="11">
+        <v>1</v>
+      </c>
+      <c r="O47" s="10">
+        <v>60</v>
+      </c>
+      <c r="P47" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="10">
+        <v>1</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="7">
+        <v>24459</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G48" s="8">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10">
+        <v>1</v>
+      </c>
+      <c r="I48" s="10">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8">
+        <v>0</v>
+      </c>
+      <c r="M48" s="10">
+        <v>1</v>
+      </c>
+      <c r="N48" s="11">
+        <v>1</v>
+      </c>
+      <c r="O48" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P48" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="10">
+        <v>1</v>
+      </c>
+      <c r="R48" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T48" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="8" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="7">
+        <v>24458</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G49" s="8">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10">
+        <v>1</v>
+      </c>
+      <c r="I49" s="10">
+        <v>1</v>
+      </c>
+      <c r="J49" s="10">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="10">
+        <v>1</v>
+      </c>
+      <c r="N49" s="11">
+        <v>1</v>
+      </c>
+      <c r="O49" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P49" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="10">
+        <v>1</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T49" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="7">
+        <v>24460</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="8">
+        <v>1</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1</v>
+      </c>
+      <c r="I50" s="10">
+        <v>1</v>
+      </c>
+      <c r="J50" s="10">
+        <v>1</v>
+      </c>
+      <c r="K50" s="8">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8">
+        <v>0</v>
+      </c>
+      <c r="M50" s="10">
+        <v>1</v>
+      </c>
+      <c r="N50" s="11">
+        <v>1</v>
+      </c>
+      <c r="O50" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P50" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="10">
+        <v>1</v>
+      </c>
+      <c r="R50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T50" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="3">
+        <v>24461</v>
+      </c>
+      <c r="C51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E51" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="2">
+        <v>1</v>
+      </c>
+      <c r="O51" s="1">
+        <v>600</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>1</v>
+      </c>
+      <c r="R51" t="s">
+        <v>18</v>
+      </c>
+      <c r="T51" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="3">
+        <v>24462</v>
+      </c>
+      <c r="C52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" t="s">
+        <v>111</v>
+      </c>
+      <c r="F52" t="s">
+        <v>148</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2">
+        <v>1</v>
+      </c>
+      <c r="O52" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>1</v>
+      </c>
+      <c r="R52" t="s">
+        <v>18</v>
+      </c>
+      <c r="T52" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="3">
+        <v>24464</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" t="s">
+        <v>113</v>
+      </c>
+      <c r="F53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>1</v>
+      </c>
+      <c r="R53" t="s">
+        <v>18</v>
+      </c>
+      <c r="T53" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="3">
+        <v>24463</v>
+      </c>
+      <c r="C54" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" t="s">
+        <v>112</v>
+      </c>
+      <c r="F54" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2">
+        <v>1</v>
+      </c>
+      <c r="O54" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>1</v>
+      </c>
+      <c r="R54" t="s">
+        <v>18</v>
+      </c>
+      <c r="T54" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="7">
+        <v>24468</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="8">
+        <v>1</v>
+      </c>
+      <c r="H55" s="10">
+        <v>1</v>
+      </c>
+      <c r="I55" s="10">
+        <v>1</v>
+      </c>
+      <c r="J55" s="10">
+        <v>1</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="10">
+        <v>1</v>
+      </c>
+      <c r="N55" s="11">
+        <v>1</v>
+      </c>
+      <c r="O55" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P55" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>1</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T55" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="7">
+        <v>24465</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G56" s="8">
+        <v>1</v>
+      </c>
+      <c r="H56" s="10">
+        <v>1</v>
+      </c>
+      <c r="I56" s="10">
+        <v>1</v>
+      </c>
+      <c r="J56" s="10">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8">
+        <v>0</v>
+      </c>
+      <c r="M56" s="10">
+        <v>1</v>
+      </c>
+      <c r="N56" s="11">
+        <v>1</v>
+      </c>
+      <c r="O56" s="10">
+        <v>94</v>
+      </c>
+      <c r="P56" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="10">
+        <v>1</v>
+      </c>
+      <c r="R56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T56" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="7">
+        <v>24466</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" s="8">
+        <v>1</v>
+      </c>
+      <c r="H57" s="10">
+        <v>1</v>
+      </c>
+      <c r="I57" s="10">
+        <v>1</v>
+      </c>
+      <c r="J57" s="10">
+        <v>1</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
+        <v>0</v>
+      </c>
+      <c r="M57" s="10">
+        <v>1</v>
+      </c>
+      <c r="N57" s="11">
+        <v>1</v>
+      </c>
+      <c r="O57" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P57" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="10">
+        <v>1</v>
+      </c>
+      <c r="R57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T57" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="7">
+        <v>24467</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" s="8">
+        <v>1</v>
+      </c>
+      <c r="H58" s="10">
+        <v>1</v>
+      </c>
+      <c r="I58" s="10">
+        <v>1</v>
+      </c>
+      <c r="J58" s="10">
+        <v>1</v>
+      </c>
+      <c r="K58" s="8">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <v>0</v>
+      </c>
+      <c r="M58" s="10">
+        <v>1</v>
+      </c>
+      <c r="N58" s="11">
+        <v>1</v>
+      </c>
+      <c r="O58" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P58" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="10">
+        <v>1</v>
+      </c>
+      <c r="R58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T58" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3">
+        <v>24471</v>
+      </c>
+      <c r="C59" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" t="s">
+        <v>116</v>
+      </c>
+      <c r="F59" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2">
+        <v>1</v>
+      </c>
+      <c r="O59" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>1</v>
+      </c>
+      <c r="R59" t="s">
+        <v>18</v>
+      </c>
+      <c r="T59" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="3">
+        <v>24469</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" t="s">
+        <v>151</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>1</v>
+      </c>
+      <c r="R60" t="s">
+        <v>18</v>
+      </c>
+      <c r="T60" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3">
+        <v>24470</v>
+      </c>
+      <c r="C61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" t="s">
+        <v>152</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>1</v>
+      </c>
+      <c r="R61" t="s">
+        <v>18</v>
+      </c>
+      <c r="T61" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>24472</v>
+      </c>
+      <c r="C62" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" t="s">
+        <v>154</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2">
+        <v>1</v>
+      </c>
+      <c r="O62" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>1</v>
+      </c>
+      <c r="R62" t="s">
+        <v>18</v>
+      </c>
+      <c r="T62" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <v>24476</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G63" s="8">
+        <v>1</v>
+      </c>
+      <c r="H63" s="10">
+        <v>1</v>
+      </c>
+      <c r="I63" s="10">
+        <v>1</v>
+      </c>
+      <c r="J63" s="10">
+        <v>1</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="10">
+        <v>1</v>
+      </c>
+      <c r="N63" s="11">
+        <v>1</v>
+      </c>
+      <c r="O63" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P63" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="10">
+        <v>1</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T63" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="7">
+        <v>24473</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G64" s="8">
+        <v>1</v>
+      </c>
+      <c r="H64" s="10">
+        <v>1</v>
+      </c>
+      <c r="I64" s="10">
+        <v>1</v>
+      </c>
+      <c r="J64" s="10">
+        <v>1</v>
+      </c>
+      <c r="K64" s="8">
+        <v>0</v>
+      </c>
+      <c r="L64" s="8">
+        <v>0</v>
+      </c>
+      <c r="M64" s="10">
+        <v>1</v>
+      </c>
+      <c r="N64" s="11">
+        <v>1</v>
+      </c>
+      <c r="O64" s="10">
+        <v>90</v>
+      </c>
+      <c r="P64" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="10">
+        <v>1</v>
+      </c>
+      <c r="R64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T64" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="7">
+        <v>24474</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G65" s="8">
+        <v>1</v>
+      </c>
+      <c r="H65" s="10">
+        <v>1</v>
+      </c>
+      <c r="I65" s="10">
+        <v>1</v>
+      </c>
+      <c r="J65" s="10">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8">
+        <v>0</v>
+      </c>
+      <c r="M65" s="10">
+        <v>1</v>
+      </c>
+      <c r="N65" s="11">
+        <v>1</v>
+      </c>
+      <c r="O65" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="10">
+        <v>1</v>
+      </c>
+      <c r="R65" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T65" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="7">
+        <v>24475</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G66" s="8">
+        <v>1</v>
+      </c>
+      <c r="H66" s="10">
+        <v>1</v>
+      </c>
+      <c r="I66" s="10">
+        <v>1</v>
+      </c>
+      <c r="J66" s="10">
+        <v>1</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="L66" s="8">
+        <v>0</v>
+      </c>
+      <c r="M66" s="10">
+        <v>1</v>
+      </c>
+      <c r="N66" s="11">
+        <v>1</v>
+      </c>
+      <c r="O66" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P66" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="10">
+        <v>1</v>
+      </c>
+      <c r="R66" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T66" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="3">
+        <v>24479</v>
+      </c>
+      <c r="C67" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" t="s">
+        <v>121</v>
+      </c>
+      <c r="F67" t="s">
+        <v>158</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>1</v>
+      </c>
+      <c r="R67" t="s">
+        <v>18</v>
+      </c>
+      <c r="T67" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="3">
+        <v>24477</v>
+      </c>
+      <c r="C68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" t="s">
+        <v>156</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>1</v>
+      </c>
+      <c r="N68" s="2">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
+        <v>125</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>1</v>
+      </c>
+      <c r="R68" t="s">
+        <v>18</v>
+      </c>
+      <c r="T68" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="3">
+        <v>24478</v>
+      </c>
+      <c r="C69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" t="s">
+        <v>157</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="N69" s="2">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>1</v>
+      </c>
+      <c r="R69" t="s">
+        <v>18</v>
+      </c>
+      <c r="T69" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="3">
+        <v>24480</v>
+      </c>
+      <c r="C70" t="s">
+        <v>204</v>
+      </c>
+      <c r="E70" t="s">
+        <v>122</v>
+      </c>
+      <c r="F70" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>1</v>
+      </c>
+      <c r="R70" t="s">
+        <v>18</v>
+      </c>
+      <c r="T70" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="7">
+        <v>24482</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G71" s="8">
+        <v>1</v>
+      </c>
+      <c r="H71" s="10">
+        <v>1</v>
+      </c>
+      <c r="I71" s="10">
+        <v>1</v>
+      </c>
+      <c r="J71" s="10">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="L71" s="8">
+        <v>0</v>
+      </c>
+      <c r="M71" s="10">
+        <v>1</v>
+      </c>
+      <c r="N71" s="11">
+        <v>1</v>
+      </c>
+      <c r="O71" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P71" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="10">
+        <v>1</v>
+      </c>
+      <c r="R71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T71" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" s="7">
+        <v>24484</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G72" s="8">
+        <v>1</v>
+      </c>
+      <c r="H72" s="10">
+        <v>1</v>
+      </c>
+      <c r="I72" s="10">
+        <v>1</v>
+      </c>
+      <c r="J72" s="10">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8">
+        <v>0</v>
+      </c>
+      <c r="L72" s="8">
+        <v>0</v>
+      </c>
+      <c r="M72" s="10">
+        <v>1</v>
+      </c>
+      <c r="N72" s="11">
+        <v>1</v>
+      </c>
+      <c r="O72" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P72" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="10">
+        <v>1</v>
+      </c>
+      <c r="R72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T72" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="7">
+        <v>24481</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G73" s="8">
+        <v>1</v>
+      </c>
+      <c r="H73" s="10">
+        <v>1</v>
+      </c>
+      <c r="I73" s="10">
+        <v>1</v>
+      </c>
+      <c r="J73" s="10">
+        <v>1</v>
+      </c>
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="L73" s="8">
+        <v>0</v>
+      </c>
+      <c r="M73" s="10">
+        <v>1</v>
+      </c>
+      <c r="N73" s="11">
+        <v>1</v>
+      </c>
+      <c r="O73" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P73" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="10">
+        <v>1</v>
+      </c>
+      <c r="R73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T73" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="7">
+        <v>24483</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G74" s="8">
+        <v>1</v>
+      </c>
+      <c r="H74" s="10">
+        <v>1</v>
+      </c>
+      <c r="I74" s="10">
+        <v>1</v>
+      </c>
+      <c r="J74" s="10">
+        <v>1</v>
+      </c>
+      <c r="K74" s="8">
+        <v>0</v>
+      </c>
+      <c r="L74" s="8">
+        <v>0</v>
+      </c>
+      <c r="M74" s="10">
+        <v>1</v>
+      </c>
+      <c r="N74" s="11">
+        <v>1</v>
+      </c>
+      <c r="O74" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P74" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="10">
+        <v>1</v>
+      </c>
+      <c r="R74" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T74" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="3">
+        <v>24487</v>
+      </c>
+      <c r="C75" t="s">
+        <v>211</v>
+      </c>
+      <c r="E75" t="s">
+        <v>163</v>
+      </c>
+      <c r="F75" t="s">
+        <v>164</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>1</v>
+      </c>
+      <c r="N75" s="2">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>1</v>
+      </c>
+      <c r="R75" t="s">
+        <v>18</v>
+      </c>
+      <c r="T75" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="3">
+        <v>24485</v>
+      </c>
+      <c r="C76" t="s">
+        <v>209</v>
+      </c>
+      <c r="E76" t="s">
+        <v>122</v>
+      </c>
+      <c r="F76" t="s">
+        <v>159</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>1</v>
+      </c>
+      <c r="N76" s="2">
+        <v>1</v>
+      </c>
+      <c r="O76" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>1</v>
+      </c>
+      <c r="R76" t="s">
+        <v>18</v>
+      </c>
+      <c r="T76" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="3">
+        <v>24488</v>
+      </c>
+      <c r="C77" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" t="s">
+        <v>166</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>1</v>
+      </c>
+      <c r="N77" s="2">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>1</v>
+      </c>
+      <c r="R77" t="s">
+        <v>18</v>
+      </c>
+      <c r="T77" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="3">
+        <v>24486</v>
+      </c>
+      <c r="C78" t="s">
+        <v>210</v>
+      </c>
+      <c r="E78" t="s">
+        <v>123</v>
+      </c>
+      <c r="F78" t="s">
+        <v>160</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>1</v>
+      </c>
+      <c r="N78" s="2">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
+        <v>1000</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>1</v>
+      </c>
+      <c r="R78" t="s">
+        <v>18</v>
+      </c>
+      <c r="T78" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="7">
+        <v>24489</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G79" s="8">
+        <v>1</v>
+      </c>
+      <c r="H79" s="10">
+        <v>1</v>
+      </c>
+      <c r="I79" s="10">
+        <v>1</v>
+      </c>
+      <c r="J79" s="10">
+        <v>1</v>
+      </c>
+      <c r="K79" s="8">
+        <v>0</v>
+      </c>
+      <c r="L79" s="8">
+        <v>0</v>
+      </c>
+      <c r="M79" s="10">
+        <v>1</v>
+      </c>
+      <c r="N79" s="11">
+        <v>1</v>
+      </c>
+      <c r="O79" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P79" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>1</v>
+      </c>
+      <c r="R79" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T79" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="7">
+        <v>24491</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G80" s="8">
+        <v>1</v>
+      </c>
+      <c r="H80" s="10">
+        <v>1</v>
+      </c>
+      <c r="I80" s="10">
+        <v>1</v>
+      </c>
+      <c r="J80" s="10">
+        <v>1</v>
+      </c>
+      <c r="K80" s="8">
+        <v>0</v>
+      </c>
+      <c r="L80" s="8">
+        <v>0</v>
+      </c>
+      <c r="M80" s="10">
+        <v>1</v>
+      </c>
+      <c r="N80" s="11">
+        <v>1</v>
+      </c>
+      <c r="O80" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P80" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>1</v>
+      </c>
+      <c r="R80" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T80" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="7">
+        <v>24490</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G81" s="8">
+        <v>1</v>
+      </c>
+      <c r="H81" s="10">
+        <v>1</v>
+      </c>
+      <c r="I81" s="10">
+        <v>1</v>
+      </c>
+      <c r="J81" s="10">
+        <v>1</v>
+      </c>
+      <c r="K81" s="8">
+        <v>0</v>
+      </c>
+      <c r="L81" s="8">
+        <v>0</v>
+      </c>
+      <c r="M81" s="10">
+        <v>1</v>
+      </c>
+      <c r="N81" s="11">
+        <v>1</v>
+      </c>
+      <c r="O81" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P81" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>1</v>
+      </c>
+      <c r="R81" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T81" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="7">
+        <v>24492</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G82" s="8">
+        <v>1</v>
+      </c>
+      <c r="H82" s="10">
+        <v>1</v>
+      </c>
+      <c r="I82" s="10">
+        <v>1</v>
+      </c>
+      <c r="J82" s="10">
+        <v>1</v>
+      </c>
+      <c r="K82" s="8">
+        <v>0</v>
+      </c>
+      <c r="L82" s="8">
+        <v>0</v>
+      </c>
+      <c r="M82" s="10">
+        <v>1</v>
+      </c>
+      <c r="N82" s="11">
+        <v>1</v>
+      </c>
+      <c r="O82" s="10">
+        <v>1000</v>
+      </c>
+      <c r="P82" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="10">
+        <v>1</v>
+      </c>
+      <c r="R82" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T82" s="8">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
